--- a/daily/2026-04-15.xlsx
+++ b/daily/2026-04-15.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00E0E0E0"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001E1E2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0022C55E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF4444"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,7 +67,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -65,6 +75,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -628,7 +640,6 @@
       <c r="V2" t="n">
         <v>29</v>
       </c>
-      <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
         <v>5.3</v>
       </c>
@@ -4597,603 +4608,1383 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>VJ Edgecombe</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>ORL @ PHI</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E2" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Edgecombe scored 19 pts vs 15.5 line (+3.5), OVER hit by 3.5 pts. Edgecombe played 42 min (+7.2 vs L10 avg of 34.7) — 21% more than expected. Shooting efficiency was cold: 43.8% FG (-6.5% vs L10 avg of 50.3%). 7/16 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, FG Trend (6/10 aligned). Counter-signals that were wrong: HR L10, Trend, H2H. Projection model targeted 16.5 pts — actual 19 was 2.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Edgecombe's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:43</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Desmond Bane</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>ORL @ PHI</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E3" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Bane scored 34 pts vs 19.5 line (+14.5), OVER hit by 14.5 pts. Bane played 40 min (+10.4 vs L10 avg of 29.3) — 35% more than expected. Shooting efficiency was hot: 62.5% FG (+17.2% vs L10 avg of 45.3%). 10/16 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, H2H (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, Pace. Projection model targeted 21.3 pts — actual 34 was 12.7 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Bane's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:43</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Kelly Oubre Jr.</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>ORL @ PHI</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E4" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Jr. scored 19 pts vs 13.5 line (+5.5), UNDER missed by 5.5 pts. Jr. played 40 min (+12.0 vs L10 avg of 28.3) — 42% more than expected. Shooting was in line with averages: 50.0% FG (6/12, L10 avg 47.1%). Counter-signals that proved correct: Volume, HR L30, FG Trend. Signals that were wrong: HR L10, Trend, Context. Projection model targeted 10.1 pts — actual 19 was 8.9 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:43</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Tyrese Maxey</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>ORL @ PHI</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="4" t="n">
         <v>29.5</v>
       </c>
+      <c r="E5" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Maxey scored 31 pts vs 29.5 line (+1.5), UNDER missed by 1.5 pts. Maxey played 42 min (+5.9 vs L10 avg of 36.5) — 16% more than expected. Shooting was in line with averages: 44.0% FG (11/25, L10 avg 48.9%). Counter-signals that proved correct: Defense, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 21.5 pts — actual 31 was 9.5 pts off (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:43</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Tristan da Silva</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>ORL @ PHI</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="4" t="n">
         <v>6.5</v>
       </c>
+      <c r="E6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Silva scored 4 pts vs 6.5 line (-2.5), OVER missed by 2.5 pts. Silva played 14 min (-11.4 vs L10 avg of 24.9) — 46% less than expected. Shooting efficiency was hot: 100.0% FG (+55.7% vs L10 avg of 44.3%). 2/2 from the field. Counter-signals that proved correct: Trend, H2H, Pace, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 7.3 pts — actual 4 was 3.3 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Silva for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:43</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Paolo Banchero</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>ORL @ PHI</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3" t="n">
         <v>22.5</v>
       </c>
+      <c r="E7" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Banchero scored 18 pts vs 22.5 line (-4.5), UNDER hit by 4.5 pts. Minutes were as expected: 36 played vs L10 avg 33.2. Shooting efficiency was cold: 31.8% FG (-13.0% vs L10 avg of 44.8%). 7/22 from the field. Signals that called it correctly: HR L10, Trend, Context, H2H, Pace (7/10 aligned). Counter-signals that were wrong: Volume, HR L30, Defense. Projection model targeted 18.1 pts — actual 18 was 0.1 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Banchero in this role.</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:43</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Franz Wagner</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>ORL @ PHI</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="4" t="n">
         <v>18.5</v>
       </c>
+      <c r="E8" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Wagner scored 12 pts vs 18.5 line (-6.5), OVER missed by 6.5 pts. Wagner played 29 min (+7.4 vs L10 avg of 21.9) — 34% more than expected. Shooting was in line with averages: 45.5% FG (5/11, L10 avg 45.0%). Counter-signals that proved correct: HR L10, Trend, Pace, FG Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 23.3 pts — actual 12 was 11.3 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Wagner's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:43</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Andre Drummond</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>ORL @ PHI</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="4" t="n">
         <v>6.5</v>
       </c>
+      <c r="E9" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Drummond scored 14 pts vs 6.5 line (+7.5), UNDER missed by 7.5 pts. Drummond played 32 min (+14.4 vs L10 avg of 17.1) — 84% more than expected. Shooting efficiency was hot: 62.5% FG (+13.8% vs L10 avg of 48.7%). 5/8 from the field. Counter-signals that proved correct: Trend, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 5.2 pts — actual 14 was 8.8 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:43</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Quentin Grimes</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>ORL @ PHI</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Grimes scored 4 pts vs 9.5 line (-5.5), UNDER hit by 5.5 pts. Grimes played 22 min (-3.1 vs L10 avg of 25.0) — 12% less than expected. Shooting efficiency was cold: 33.3% FG (-6.6% vs L10 avg of 39.9%). 1/3 from the field. Signals that called it correctly: Trend, H2H, Pace, FG Trend, Min Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 6.6 pts — actual 4 was 2.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Grimes's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:43</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Wendell Carter Jr.</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>ORL @ PHI</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E11" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Jr. scored 5 pts vs 10.5 line (-5.5), UNDER hit by 5.5 pts. Jr. played 32 min (+4.2 vs L10 avg of 27.7) — 15% more than expected. Shooting efficiency was cold: 14.3% FG (-35.1% vs L10 avg of 49.4%). 1/7 from the field. Signals that called it correctly: Trend, H2H, Pace, FG Trend, Min Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 9.6 pts — actual 5 was 4.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Jr.'s consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:43</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Jalen Suggs</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>ORL @ PHI</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E12" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Suggs scored 4 pts vs 14.5 line (-10.5), UNDER hit by 10.5 pts. Suggs played 37 min (+6.8 vs L10 avg of 30.6) — 22% more than expected. Shooting efficiency was cold: 11.1% FG (-33.4% vs L10 avg of 44.5%). 1/9 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Pace (5/10 aligned). Counter-signals that were wrong: Trend, Defense, H2H. Projection model targeted 11.5 pts — actual 4 was 7.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Suggs's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:43</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Anthony Black</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>ORL @ PHI</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E13" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Black scored 13 pts vs 9.5 line (+3.5), OVER hit by 3.5 pts. Minutes were as expected: 22 played vs L10 avg 22.9. Shooting efficiency was hot: 50.0% FG (+20.0% vs L10 avg of 30.0%). 4/8 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, H2H (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, Pace. Projection model targeted 16.1 pts — actual 13 was 3.1 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Black's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:43</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Paul George</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>ORL @ PHI</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="3" t="n">
         <v>21.5</v>
       </c>
+      <c r="E14" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>WIN — George scored 16 pts vs 21.5 line (-5.5), UNDER hit by 5.5 pts. George played 36 min (+4.9 vs L10 avg of 31.1) — 16% more than expected. Shooting efficiency was cold: 37.5% FG (-8.2% vs L10 avg of 45.7%). 6/16 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (9/10 aligned). Counter-signals that were wrong: FG Trend. Projection model targeted 20.6 pts — actual 16 was 4.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (9/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:43</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Adem Bona</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>ORL @ PHI</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="3" t="n">
         <v>4.5</v>
       </c>
+      <c r="E15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Bona scored 2 pts vs 4.5 line (-2.5), UNDER hit by 2.5 pts. Minutes were as expected: 16 played vs L10 avg 16.3. Shooting efficiency was cold: 0.0% FG (-55.0% vs L10 avg of 55.0%). 0/1 from the field. Signals that called it correctly: HR L10, Trend, Defense, H2H, Pace (7/10 aligned). Counter-signals that were wrong: Volume, HR L30, Context. Projection model targeted 2.5 pts — actual 2 was 0.5 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Bona in this role.</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:43</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Dominick Barlow</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>ORL @ PHI</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="4" t="n">
         <v>5.5</v>
       </c>
+      <c r="E16" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Barlow scored 4 pts vs 5.5 line (-1.5), OVER missed by 1.5 pts. Barlow played 10 min (-11.6 vs L10 avg of 21.6) — 54% less than expected. Shooting efficiency was cold: 50.0% FG (-17.7% vs L10 avg of 67.7%). 2/4 from the field. Counter-signals that proved correct: Trend, Defense, Pace, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 8.2 pts — actual 4 was 4.2 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Barlow for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:43</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Kawhi Leonard</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>GSW @ LAC</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="3" t="n">
         <v>29.5</v>
       </c>
+      <c r="E17" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Leonard scored 21 pts vs 29.5 line (-8.5), UNDER hit by 8.5 pts. Leonard played 40 min (+9.5 vs L10 avg of 30.7) — 31% more than expected. Shooting was in line with averages: 47.1% FG (8/17, L10 avg 50.3%). Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (9/10 aligned). Counter-signals that were wrong: Pace. Projection model targeted 27.0 pts — actual 21 was 6.0 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (9/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:43</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Stephen Curry</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>GSW @ LAC</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="4" t="n">
         <v>26.5</v>
       </c>
+      <c r="E18" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Curry scored 35 pts vs 26.5 line (+8.5), UNDER missed by 8.5 pts. Curry played 36 min (+8.3 vs L10 avg of 27.5) — 30% more than expected. Shooting efficiency was hot: 52.2% FG (+7.2% vs L10 avg of 45.0%). 12/23 from the field. Counter-signals that proved correct: HR L30, Defense. Signals that were wrong: Volume, HR L10, Trend. Projection model targeted 22.2 pts — actual 35 was 12.8 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:43</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Darius Garland</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>GSW @ LAC</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="4" t="n">
         <v>20.5</v>
       </c>
+      <c r="E19" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Garland scored 21 pts vs 20.5 line (+0.5), UNDER missed by 0.5 pts. Minutes were as expected: 31 played vs L10 avg 29.5. Shooting efficiency was hot: 53.3% FG (+6.0% vs L10 avg of 47.3%). 8/15 from the field. Counter-signals that proved correct: Defense, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 14.8 pts — actual 21 was 6.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:43</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Kristaps Porziņģis</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>GSW @ LAC</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="4" t="n">
         <v>18.5</v>
       </c>
+      <c r="E20" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Porziņģis scored 20 pts vs 18.5 line (+1.5), UNDER missed by 1.5 pts. Minutes were as expected: 28 played vs L10 avg 24.8. Shooting efficiency was hot: 66.7% FG (+27.0% vs L10 avg of 39.7%). 8/12 from the field. Counter-signals that proved correct: Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 11.0 pts — actual 20 was 9.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:43</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Brandin Podziemski</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>GSW @ LAC</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E21" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Podziemski scored 17 pts vs 13.5 line (+3.5), OVER hit by 3.5 pts. Podziemski played 40 min (+10.9 vs L10 avg of 29.6) — 37% more than expected. Shooting efficiency was cold: 45.5% FG (-5.9% vs L10 avg of 51.4%). 5/11 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: H2H, Pace, Min Trend. Projection model targeted 15.4 pts — actual 17 was 1.6 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Podziemski in this role.</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:43</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>De'Anthony Melton</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>GSW @ LAC</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E22" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Melton scored 7 pts vs 11.5 line (-4.5), UNDER hit by 4.5 pts. Minutes were as expected: 23 played vs L10 avg 23.7. Shooting efficiency was hot: 42.9% FG (+12.3% vs L10 avg of 30.6%). 3/7 from the field. Signals that called it correctly: HR L10, Trend, H2H, Pace, FG Trend (6/10 aligned). Counter-signals that were wrong: Volume, HR L30, Context. Projection model targeted 6.6 pts — actual 7 was 0.4 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Melton in this role.</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:43</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Bennedict Mathurin</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>GSW @ LAC</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E23" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Mathurin scored 23 pts vs 11.5 line (+11.5), OVER hit by 11.5 pts. Mathurin played 30 min (+5.0 vs L10 avg of 24.8) — 20% more than expected. Shooting efficiency was hot: 63.6% FG (+27.1% vs L10 avg of 36.5%). 7/11 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, H2H (6/10 aligned). Counter-signals that were wrong: HR L10, Trend, FG Trend. Projection model targeted 18.9 pts — actual 23 was 4.1 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Mathurin's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:43</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>John Collins</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>GSW @ LAC</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E24" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Collins scored 11 pts vs 11.5 line (-0.5), UNDER hit by 0.5 pts. Collins played 21 min (-3.5 vs L10 avg of 24.7) — 14% less than expected. Shooting efficiency was hot: 62.5% FG (+15.7% vs L10 avg of 46.8%). 5/8 from the field. Signals that called it correctly: Trend, Defense, FG Trend, Min Trend (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 10.6 pts — actual 11 was 0.4 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Collins in this role.</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:43</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Gui Santos</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>GSW @ LAC</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E25" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Santos scored 20 pts vs 10.5 line (+9.5), UNDER missed by 9.5 pts. Minutes were as expected: 32 played vs L10 avg 29.7. Shooting efficiency was hot: 69.2% FG (+25.6% vs L10 avg of 43.6%). 9/13 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, Defense, H2H. Projection model targeted 8.1 pts — actual 20 was 11.9 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:43</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Brook Lopez</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>GSW @ LAC</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E26" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Lopez scored 17 pts vs 10.5 line (+6.5), UNDER missed by 6.5 pts. Lopez played 37 min (+9.5 vs L10 avg of 27.7) — 34% more than expected. Shooting was in line with averages: 43.8% FG (7/16, L10 avg 47.1%). Counter-signals that proved correct: Volume, HR L10, Trend, Defense. Signals that were wrong: HR L30, Context, H2H. Projection model targeted 5.8 pts — actual 17 was 11.2 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Lopez's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:43</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Derrick Jones Jr.</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>GSW @ LAC</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E27" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Jr. scored 13 pts vs 8.5 line (+4.5), UNDER missed by 4.5 pts. Minutes were as expected: 23 played vs L10 avg 25.0. Shooting efficiency was hot: 55.6% FG (+18.3% vs L10 avg of 37.3%). 5/9 from the field. Counter-signals that proved correct: Volume, HR L30, Context, Pace. Signals that were wrong: HR L10, Trend, Defense. Projection model targeted 6.7 pts — actual 13 was 6.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:43</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>Draymond Green</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>GSW @ LAC</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E28" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Green scored 7 pts vs 8.5 line (-1.5), UNDER hit by 1.5 pts. Green played 35 min (+5.7 vs L10 avg of 29.6) — 19% more than expected. Shooting efficiency was hot: 60.0% FG (+18.3% vs L10 avg of 41.7%). 3/5 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (8/10 aligned). Counter-signals that were wrong: FG Trend, Min Trend. Projection model targeted 6.5 pts — actual 7 was 0.5 pts close (correct direction). Result classification: CLOSE_CALL. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:43</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Gary Payton II</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>GSW @ LAC</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="4" t="n">
         <v>6.5</v>
       </c>
+      <c r="E29" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — II scored 6 pts vs 6.5 line (-0.5), OVER missed by 0.5 pts. Minutes were as expected: 24 played vs L10 avg 21.0. Shooting efficiency was cold: 50.0% FG (-25.5% vs L10 avg of 75.5%). 2/4 from the field. Counter-signals that proved correct: Trend, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 6.4 pts — actual 6 was 0.4 pts close (wrong direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:43</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Kris Dunn</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>GSW @ LAC</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="3" t="n">
         <v>6.5</v>
       </c>
+      <c r="E30" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Dunn scored 7 pts vs 6.5 line (+0.5), OVER hit by 0.5 pts. Dunn played 32 min (+7.7 vs L10 avg of 24.7) — 31% more than expected. Shooting efficiency was hot: 60.0% FG (+19.9% vs L10 avg of 40.1%). 3/5 from the field. Signals that called it correctly: Context, Defense, H2H, Pace (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 9.1 pts — actual 7 was 2.1 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Dunn's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:43</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>Al Horford</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>GSW @ LAC</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="3" t="n">
         <v>5.5</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Horford scored 14 pts vs 5.5 line (+8.5), OVER hit by 8.5 pts. Minutes were as expected: 22 played vs L10 avg 24.1. Shooting efficiency was hot: 62.5% FG (+16.9% vs L10 avg of 45.6%). 5/8 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (6/10 aligned). Counter-signals that were wrong: Trend, Defense, Pace. Projection model targeted 6.5 pts — actual 14 was 7.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Horford's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:43</t>
+        </is>
       </c>
     </row>
   </sheetData>
